--- a/data/trans_dic/P1429-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1429-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,44</t>
+          <t>0,23; 2,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,64</t>
+          <t>0,26; 1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,41</t>
+          <t>1,8; 6,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,23</t>
+          <t>0,61; 3,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,36</t>
+          <t>0,91; 4,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,26</t>
+          <t>1,79; 4,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,97</t>
+          <t>1,07; 3,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,98</t>
+          <t>0,38; 2,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,44</t>
+          <t>0,65; 2,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,53</t>
+          <t>1,12; 2,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,03</t>
+          <t>0,22; 2,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,24</t>
+          <t>0,78; 4,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,03</t>
+          <t>0,3; 2,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,31</t>
+          <t>0,34; 3,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,76</t>
+          <t>2,11; 4,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,55</t>
+          <t>0,67; 2,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,47</t>
+          <t>0,13; 1,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,7</t>
+          <t>0,17; 1,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,32</t>
+          <t>1,02; 2,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,4</t>
+          <t>0,34; 2,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,75</t>
+          <t>0,19; 1,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,84</t>
+          <t>0,4; 2,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,8</t>
+          <t>1,85; 8,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,96</t>
+          <t>1,02; 5,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 11,04</t>
+          <t>2,22; 11,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,54</t>
+          <t>4,84; 13,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,09</t>
+          <t>0,99; 3,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,09</t>
+          <t>0,45; 2,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,31</t>
+          <t>0,96; 3,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,65</t>
+          <t>1,99; 4,98</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,23</t>
+          <t>0,83; 2,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,92</t>
+          <t>0,82; 2,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,06</t>
+          <t>2,29; 4,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,76</t>
+          <t>0,82; 2,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,36</t>
+          <t>1,2; 3,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,69</t>
+          <t>2,49; 4,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,79</t>
+          <t>1,61; 2,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,19</t>
+          <t>0,43; 1,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,54</t>
+          <t>0,58; 1,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,91</t>
+          <t>1,7; 2,96</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,89</t>
+          <t>0,31; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,56</t>
+          <t>0,28; 1,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,17</t>
+          <t>0,12; 1,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,63</t>
+          <t>2,34; 5,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,25</t>
+          <t>4,0; 7,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,42</t>
+          <t>1,75; 4,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,97</t>
+          <t>5,01; 7,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,9</t>
+          <t>1,71; 3,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,58</t>
+          <t>2,46; 4,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,65</t>
+          <t>1,19; 2,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,55</t>
+          <t>3,17; 4,73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,39</t>
+          <t>4,55; 7,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,23</t>
+          <t>5,0; 8,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,22</t>
+          <t>4,3; 7,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,7</t>
+          <t>4,88; 7,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,96</t>
+          <t>3,68; 5,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,46</t>
+          <t>4,11; 6,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,77</t>
+          <t>3,36; 5,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,86</t>
+          <t>3,86; 5,96</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,41</t>
+          <t>0,73; 1,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,45</t>
+          <t>0,06; 0,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,57</t>
+          <t>0,18; 0,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,33</t>
+          <t>0,58; 1,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 5,01</t>
+          <t>3,63; 4,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,73</t>
+          <t>3,38; 4,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,14</t>
+          <t>2,86; 4,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,11</t>
+          <t>4,24; 5,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,11</t>
+          <t>2,3; 3,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,49</t>
+          <t>1,8; 2,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,3</t>
+          <t>1,59; 2,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,03</t>
+          <t>2,51; 3,17</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>17617</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1470; 11545</t>
+          <t>1072; 11292</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5870</t>
+          <t>0; 4821</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6734</t>
+          <t>0; 6617</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1245; 8236</t>
+          <t>1409; 9217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5779; 19645</t>
+          <t>5532; 18847</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1956; 13314</t>
+          <t>1915; 12528</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3176; 15140</t>
+          <t>3165; 14486</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8197; 19025</t>
+          <t>8738; 19674</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7864; 23184</t>
+          <t>8318; 23961</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2892; 14830</t>
+          <t>2822; 15439</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4606; 18962</t>
+          <t>5070; 18009</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11333; 24029</t>
+          <t>11554; 24771</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>14060</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>807; 7451</t>
+          <t>810; 7375</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2879</t>
+          <t>0; 2755</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3225; 15750</t>
+          <t>2894; 14881</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1050; 10247</t>
+          <t>1003; 10028</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1242; 12336</t>
+          <t>1262; 13070</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7445; 18137</t>
+          <t>8906; 19699</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5400; 18867</t>
+          <t>4924; 17685</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1912; 11143</t>
+          <t>984; 9318</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1813; 12731</t>
+          <t>1244; 12256</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8130; 19325</t>
+          <t>9230; 20682</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>19948</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1881; 13009</t>
+          <t>1855; 13882</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 13288</t>
+          <t>0; 9585</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>992; 9128</t>
+          <t>1006; 9288</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1181; 12305</t>
+          <t>1864; 10251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3331; 14757</t>
+          <t>3102; 13835</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2674; 12893</t>
+          <t>2645; 14054</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3759; 18334</t>
+          <t>3688; 18661</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8453; 22601</t>
+          <t>9077; 25197</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6975; 21968</t>
+          <t>7003; 22652</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3282; 18612</t>
+          <t>3982; 18612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6446; 22746</t>
+          <t>6607; 22717</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6814; 30493</t>
+          <t>13114; 32752</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15835</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41180</t>
+          <t>43899</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10542; 27652</t>
+          <t>10296; 27025</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6947</t>
+          <t>0; 6966</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6933</t>
+          <t>0; 7366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9242; 30169</t>
+          <t>9282; 31771</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16637; 36151</t>
+          <t>16361; 35543</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7147; 21120</t>
+          <t>6292; 20787</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10305; 27786</t>
+          <t>9921; 26419</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10636; 35977</t>
+          <t>21285; 36208</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30451; 54545</t>
+          <t>31384; 55964</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8208; 22860</t>
+          <t>8204; 23455</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11427; 30434</t>
+          <t>11547; 29684</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27981; 58429</t>
+          <t>33718; 58760</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45855</t>
+          <t>51278</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48182</t>
+          <t>53899</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1053; 10137</t>
+          <t>1096; 10286</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5402</t>
+          <t>0; 5343</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1692; 9671</t>
+          <t>1725; 9630</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>607; 5545</t>
+          <t>705; 6295</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12912; 32041</t>
+          <t>13308; 32140</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31516; 55086</t>
+          <t>30420; 56493</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12973; 32657</t>
+          <t>12934; 32238</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33530; 58222</t>
+          <t>41462; 61383</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16194; 35882</t>
+          <t>15754; 35541</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30935; 58145</t>
+          <t>31314; 57304</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16334; 35976</t>
+          <t>16151; 37759</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38266; 59597</t>
+          <t>44091; 65907</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>47277</t>
+          <t>51401</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47767</t>
+          <t>51919</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3430</t>
+          <t>0; 3093</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58887; 92288</t>
+          <t>56775; 92921</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55207; 91168</t>
+          <t>55394; 89112</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45641; 78154</t>
+          <t>46550; 78984</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>39031; 58467</t>
+          <t>41080; 62664</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58516; 92270</t>
+          <t>56931; 91937</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54284; 88801</t>
+          <t>56544; 90715</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46064; 79042</t>
+          <t>45994; 78343</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38846; 58571</t>
+          <t>41684; 64351</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>157018</t>
+          <t>172617</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>184651</t>
+          <t>201342</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23195; 45950</t>
+          <t>23796; 46624</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2067; 15244</t>
+          <t>2062; 14233</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6285; 19336</t>
+          <t>6168; 20357</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17967; 44789</t>
+          <t>19839; 42213</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>124433; 169290</t>
+          <t>122654; 168304</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>119391; 167586</t>
+          <t>119863; 168158</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99667; 146172</t>
+          <t>100870; 145879</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>128417; 181991</t>
+          <t>153431; 193613</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154553; 206959</t>
+          <t>153227; 207309</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>123385; 173768</t>
+          <t>125264; 175936</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109252; 159063</t>
+          <t>109823; 159221</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>154301; 210175</t>
+          <t>177467; 223610</t>
         </is>
       </c>
     </row>
